--- a/Sistema de Facturacion y Nomina de Empleados.xlsx
+++ b/Sistema de Facturacion y Nomina de Empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B477245-C39E-4D96-9F3A-884F2F9B15CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1B477245-C39E-4D96-9F3A-884F2F9B15CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB605FB-D77E-41B4-8BEE-15D62B385718}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="12372" windowHeight="12240" xr2:uid="{1AADD197-9328-46D8-85B1-0880F737AA8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{1AADD197-9328-46D8-85B1-0880F737AA8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
   <si>
     <t>Departamento</t>
   </si>
@@ -348,9 +348,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="[$$-1C0A]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="[$$-1C0A]#,##0.00"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -472,48 +472,420 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="78">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -522,11 +894,48 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -562,37 +971,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -714,24 +1097,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -912,52 +1277,52 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3EBB878-3071-4228-9DC3-E5FA0E540958}" name="Table1" displayName="Table1" ref="A3:D11" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3EBB878-3071-4228-9DC3-E5FA0E540958}" name="Table1" displayName="Table1" ref="A3:D11" totalsRowShown="0" headerRowDxfId="77" dataDxfId="76">
   <autoFilter ref="A3:D11" xr:uid="{F3EBB878-3071-4228-9DC3-E5FA0E540958}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AC270179-B770-4A55-89C3-366393ADC710}" name="ID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{A59FA3E5-3E5E-4B46-A8C5-38A2E10F648D}" name="Producto" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{74DBE885-62F6-48FC-97BE-90A6D263DDCA}" name="Precio" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{96C4342D-38D2-4AB5-85E0-14BC57828CBB}" name="Categoria" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{AC270179-B770-4A55-89C3-366393ADC710}" name="ID" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{A59FA3E5-3E5E-4B46-A8C5-38A2E10F648D}" name="Producto" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{74DBE885-62F6-48FC-97BE-90A6D263DDCA}" name="Precio" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{96C4342D-38D2-4AB5-85E0-14BC57828CBB}" name="Categoria" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19979006-B11F-4BCF-90F2-86E3AD3DD8CC}" name="Table2" displayName="Table2" ref="A1:D6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19979006-B11F-4BCF-90F2-86E3AD3DD8CC}" name="Table2" displayName="Table2" ref="A1:D6" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="A1:D6" xr:uid="{19979006-B11F-4BCF-90F2-86E3AD3DD8CC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E94E84D2-5AD0-4675-8CA6-DA732E039C59}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{766E3D87-BE6B-4552-BE11-480444A70460}" name="Nombre" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{91F7F672-305D-452C-AC19-5BD570EE8FC3}" name="Telefono" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{90E83430-8DC5-4ED9-B100-B02078E0B45F}" name="Ciudad" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{E94E84D2-5AD0-4675-8CA6-DA732E039C59}" name="ID" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{766E3D87-BE6B-4552-BE11-480444A70460}" name="Nombre" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{91F7F672-305D-452C-AC19-5BD570EE8FC3}" name="Telefono" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{90E83430-8DC5-4ED9-B100-B02078E0B45F}" name="Ciudad" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{05CEEAD6-D8EF-4D38-BBE5-5291BA23C2A1}" name="Table3" displayName="Table3" ref="A4:E9" totalsRowShown="0" headerRowDxfId="10" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{05CEEAD6-D8EF-4D38-BBE5-5291BA23C2A1}" name="Table3" displayName="Table3" ref="A4:E9" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="A4:E9" xr:uid="{05CEEAD6-D8EF-4D38-BBE5-5291BA23C2A1}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{107FF9AB-70BE-4782-94AE-2FE0AEBF80BA}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{B0C4D7AE-CCC0-44D9-A433-949FC1A7925F}" name="Nombre" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{401D7B0D-EC92-4521-A7F1-2C3A8C59AE26}" name="Cargo" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{CFC7E71E-23D1-482A-B86C-9795C38B9668}" name="Departamento" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{076BBFD2-0C73-47B2-9DFB-64ABEA499F64}" name="Salario Base" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{107FF9AB-70BE-4782-94AE-2FE0AEBF80BA}" name="ID" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{B0C4D7AE-CCC0-44D9-A433-949FC1A7925F}" name="Nombre" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{401D7B0D-EC92-4521-A7F1-2C3A8C59AE26}" name="Cargo" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{CFC7E71E-23D1-482A-B86C-9795C38B9668}" name="Departamento" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{076BBFD2-0C73-47B2-9DFB-64ABEA499F64}" name="Salario Base" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9857F08D-90F7-40C8-A75A-BE1F169DA021}" name="Table5" displayName="Table5" ref="A1:C6" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9857F08D-90F7-40C8-A75A-BE1F169DA021}" name="Table5" displayName="Table5" ref="A1:C6" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A1:C6" xr:uid="{9857F08D-90F7-40C8-A75A-BE1F169DA021}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8322CC01-820B-411F-A501-D323DBC0EB08}" name="Deduccion" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{C17891BE-BEA8-42B1-B081-9D3F45FDA524}" name="Porcentaje" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{17FC8646-CD47-424B-B45A-DFB276E2D8DF}" name="Descricpion" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{8322CC01-820B-411F-A501-D323DBC0EB08}" name="Deduccion" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{C17891BE-BEA8-42B1-B081-9D3F45FDA524}" name="Porcentaje" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{17FC8646-CD47-424B-B45A-DFB276E2D8DF}" name="Descricpion" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1273,137 +1638,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>4500</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>800</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>1500</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>3500</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>8000</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>12000</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>8500</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>2500</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1434,86 +1799,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1531,7 +1896,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -1540,443 +1905,590 @@
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:18" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>46190</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="11" t="str">
+      <c r="B5" s="8" t="str">
         <f>_xlfn.XLOOKUP(B4,Clientes!A:A,Clientes!B:B,"Cliente no encontrado")</f>
         <v xml:space="preserve">Pedro Santos </v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="11" t="str">
+      <c r="B6" s="8" t="str">
         <f>_xlfn.XLOOKUP(B4,Clientes!A:A,Clientes!D:D,"Ciudad no encontrada")</f>
         <v>Bonao</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="N9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="O9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="P9" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="Q9" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="R9" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="N10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="14" t="str">
+      <c r="O10" s="11" t="str">
+        <f>_xlfn.XLOOKUP(N10,Productos!N:N,Productos!O:O,"Producto no encontrado")</f>
+        <v>Producto no encontrado</v>
+      </c>
+      <c r="P10" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="10">
+        <f>_xlfn.XLOOKUP(N10,Productos!N:N,Productos!P:P,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <f>P10*Q10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="11" t="str">
         <f>_xlfn.XLOOKUP(A11,Productos!A:A,Productos!B:B,"Producto no encontrado")</f>
         <v>Laptop</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="11">
         <v>2</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="10">
         <f>_xlfn.XLOOKUP(A11,Productos!A:A,Productos!C:C,0)</f>
         <v>4500</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <f>C11*D11</f>
         <v>9000</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="N11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="14" t="str">
+      <c r="O11" s="11" t="str">
+        <f>_xlfn.XLOOKUP(N11,Productos!N:N,Productos!O:O,"Producto no encontrado")</f>
+        <v>Producto no encontrado</v>
+      </c>
+      <c r="P11" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="10">
+        <f>_xlfn.XLOOKUP(N11,Productos!N:N,Productos!P:P,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <f t="shared" ref="R11:R14" si="0">P11*Q11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="11" t="str">
         <f>_xlfn.XLOOKUP(A12,Productos!A:A,Productos!B:B,"Producto no encontrado")</f>
         <v>Mouse</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="11">
         <v>1</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="10">
         <f>_xlfn.XLOOKUP(A12,Productos!A:A,Productos!C:C,0)</f>
         <v>800</v>
       </c>
-      <c r="E12" s="13">
-        <f t="shared" ref="E12:E15" si="0">C12*D12</f>
+      <c r="E12" s="10">
+        <f t="shared" ref="E12:E15" si="1">C12*D12</f>
         <v>800</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="N12" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="14" t="str">
+      <c r="O12" s="11" t="str">
+        <f>_xlfn.XLOOKUP(N12,Productos!N:N,Productos!O:O,"Producto no encontrado")</f>
+        <v>Producto no encontrado</v>
+      </c>
+      <c r="P12" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="10">
+        <f>_xlfn.XLOOKUP(N12,Productos!N:N,Productos!P:P,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11" t="str">
         <f>_xlfn.XLOOKUP(A13,Productos!A:A,Productos!B:B,"Producto no encontrado")</f>
         <v>Teclado</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="11">
         <v>3</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="10">
         <f>_xlfn.XLOOKUP(A13,Productos!A:A,Productos!C:C,0)</f>
         <v>1500</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="N13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="O13" s="11" t="str">
+        <f>_xlfn.XLOOKUP(N13,Productos!N:N,Productos!O:O,"Producto no encontrado")</f>
+        <v>Producto no encontrado</v>
+      </c>
+      <c r="P13" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="10">
+        <f>_xlfn.XLOOKUP(N13,Productos!N:N,Productos!P:P,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="10">
         <f t="shared" si="0"/>
-        <v>4500</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="14" t="str">
+      <c r="B14" s="11" t="str">
         <f>_xlfn.XLOOKUP(A14,Productos!A:A,Productos!B:B,"Producto no encontrado")</f>
         <v>Silla</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="11">
         <v>1</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <f>_xlfn.XLOOKUP(A14,Productos!A:A,Productos!C:C,0)</f>
         <v>3500</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="N14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="11" t="str">
+        <f>_xlfn.XLOOKUP(N14,Productos!N:N,Productos!O:O,"Producto no encontrado")</f>
+        <v>Producto no encontrado</v>
+      </c>
+      <c r="P14" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="10">
+        <f>_xlfn.XLOOKUP(N14,Productos!N:N,Productos!P:P,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="10">
         <f t="shared" si="0"/>
-        <v>3500</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="14" t="str">
+      <c r="B15" s="11" t="str">
         <f>_xlfn.XLOOKUP(A15,Productos!A:A,Productos!B:B,"Producto no encontrado")</f>
         <v>Escritorio</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="11">
         <v>2</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="10">
         <f>_xlfn.XLOOKUP(A15,Productos!A:A,Productos!C:C,0)</f>
         <v>8000</v>
       </c>
-      <c r="E15" s="13">
-        <f t="shared" si="0"/>
+      <c r="E15" s="10">
+        <f t="shared" si="1"/>
         <v>16000</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16" s="10">
+        <f>SUM(R10:R14)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="15" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <f>SUM(E11:E15)</f>
         <v>33800</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="str">
+        <f>_xlfn.XLOOKUP(A2,Clientes!A:A,Clientes!B:B,"Cliente no encontrado")</f>
+        <v>Cliente no encontrado</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="N1:R8 N17:R1048576">
+    <cfRule type="expression" dxfId="45" priority="9">
+      <formula>"MOD(ROW();2=0"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N17:R17">
+    <cfRule type="expression" dxfId="40" priority="7">
+      <formula>"MOD(ROW();2=0"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="6">
+      <formula>"MOD(ROW();2)=0"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N9:R16">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="B2" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -1999,371 +2511,371 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>45000</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>55000</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>65000</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>50000</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>70000</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2391,152 +2903,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="13">
         <v>2.87E-2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>3.04E-2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="14">
         <v>0.1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>7.0900000000000005E-2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2551,7 +3063,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A2:H7"/>
+  <dimension ref="A2:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -2562,209 +3074,236 @@
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="19" t="str" cm="1">
+      <c r="B3" s="16" t="str" cm="1">
         <f t="array" ref="B3">_xlfn.XLOOKUP(A3,Empleados!A:A,Empleados!B:B, Empleados no encontrado)</f>
         <v>Juan Perez</v>
       </c>
-      <c r="C3" s="19" t="str">
+      <c r="C3" s="16" t="str">
         <f>_xlfn.XLOOKUP(A3,Empleados!A:A,Empleados!C:C,"Cargo No encontrado")</f>
         <v>Analista</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="17">
         <f>_xlfn.XLOOKUP(A3,Empleados!A:A,Empleados!E:E, "No encontrado")</f>
         <v>45000</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="17">
         <f>D3*_xlfn.XLOOKUP("AFP",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1291.5</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="18">
         <f>D3*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1368</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="17">
         <f>D3*_xlfn.XLOOKUP("ISR",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>4500</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="17">
         <f>D3-E3-F3-G3</f>
         <v>37840.5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="19" t="str" cm="1">
+      <c r="B4" s="16" t="str" cm="1">
         <f t="array" ref="B4">_xlfn.XLOOKUP(A4,Empleados!A:A,Empleados!B:B, Empleados no encontrado)</f>
         <v>Maria Lopez</v>
       </c>
-      <c r="C4" s="19" t="str">
+      <c r="C4" s="16" t="str">
         <f>_xlfn.XLOOKUP(A4,Empleados!A:A,Empleados!C:C,"Cargo No encontrado")</f>
         <v>Tecnico</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <f>_xlfn.XLOOKUP(A4,Empleados!A:A,Empleados!E:E, "No encontrado")</f>
         <v>55000</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="17">
         <f>D4*_xlfn.XLOOKUP("AFP",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1578.5</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="18">
         <f>D4*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1672</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="17">
         <f>D4*_xlfn.XLOOKUP("ISR",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>5500</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="17">
         <f t="shared" ref="H4:H7" si="0">D4-E4-F4-G4</f>
         <v>46249.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="19" t="str" cm="1">
+      <c r="B5" s="16" t="str" cm="1">
         <f t="array" ref="B5">_xlfn.XLOOKUP(A5,Empleados!A:A,Empleados!B:B, Empleados no encontrado)</f>
         <v>Carlos Ruiz</v>
       </c>
-      <c r="C5" s="19" t="str">
+      <c r="C5" s="16" t="str">
         <f>_xlfn.XLOOKUP(A5,Empleados!A:A,Empleados!C:C,"Cargo No encontrado")</f>
         <v>Coordinador</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="17">
         <f>_xlfn.XLOOKUP(A5,Empleados!A:A,Empleados!E:E, "No encontrado")</f>
         <v>65000</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="17">
         <f>D5*_xlfn.XLOOKUP("AFP",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1865.5</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="18">
         <f>D5*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1976</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="17">
         <f>D5*_xlfn.XLOOKUP("ISR",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>6500</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="17">
         <f t="shared" si="0"/>
         <v>54658.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="19" t="str" cm="1">
+      <c r="B6" s="16" t="str" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP(A6,Empleados!A:A,Empleados!B:B, Empleados no encontrado)</f>
         <v>Ana Garcia</v>
       </c>
-      <c r="C6" s="19" t="str">
+      <c r="C6" s="16" t="str">
         <f>_xlfn.XLOOKUP(A6,Empleados!A:A,Empleados!C:C,"Cargo No encontrado")</f>
         <v>Analista</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="17">
         <f>_xlfn.XLOOKUP(A6,Empleados!A:A,Empleados!E:E, "No encontrado")</f>
         <v>50000</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="17">
         <f>D6*_xlfn.XLOOKUP("AFP",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1435</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="18">
         <f>D6*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>1520</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="17">
         <f>D6*_xlfn.XLOOKUP("ISR",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>5000</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="17">
         <f t="shared" si="0"/>
         <v>42045</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="19" t="str" cm="1">
+      <c r="B7" s="16" t="str" cm="1">
         <f t="array" ref="B7">_xlfn.XLOOKUP(A7,Empleados!A:A,Empleados!B:B, Empleados no encontrado)</f>
         <v>Pedro Santos</v>
       </c>
-      <c r="C7" s="19" t="str">
+      <c r="C7" s="16" t="str">
         <f>_xlfn.XLOOKUP(A7,Empleados!A:A,Empleados!C:C,"Cargo No encontrado")</f>
         <v>Supervisor</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="17">
         <f>_xlfn.XLOOKUP(A7,Empleados!A:A,Empleados!E:E, "No encontrado")</f>
         <v>70000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="17">
         <f>D7*_xlfn.XLOOKUP("AFP",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>2009</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="18">
         <f>D7*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>2128</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="17">
         <f>D7*_xlfn.XLOOKUP("ISR",Deducciones!A:A,Deducciones!B:B,0)</f>
         <v>7000</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="17">
         <f t="shared" si="0"/>
         <v>58863</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I13" s="22">
+        <f>D5*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I14" s="22">
+        <f>D6*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="22">
+        <f>D7*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I16" s="22">
+        <f>D8*_xlfn.XLOOKUP("SFS",Deducciones!A:A,Deducciones!B:B,0)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A3:XFD3">
-    <cfRule type="expression" priority="3">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="A3:H7">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H7">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="A3:XFD3">
+    <cfRule type="expression" dxfId="52" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
